--- a/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -1273,7 +1273,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3.1 BoK IS2020 (19 Bahan Kajian)</t>
+          <t>3.1 BoK IS2020 (21 Bahan Kajian)</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1722,99 +1722,99 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>3.2 BoK IT2017 (14 Bahan Kajian Utama)</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="5" t="n"/>
-    </row>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS20</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Ethics, Use and Implications for Society</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>KK4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS21</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Internship and Professional Practice</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>— *(membina `S1` &amp; `KU1`–`KU3`)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>3.2 BoK IT2017 (15 Bahan Kajian Utama)</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Kode BK</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Nama Bahan Kajian IT2017</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>CPL KK Terkait</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>BK-IT01</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>Information Technology Fundamentals</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>KK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>BK-IT02</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Applied AI &amp; Intelligent Technologies</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>KK1</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>BK-IT03</t>
+          <t>BK-IT01</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Networking &amp; Communications</t>
+          <t>Information Technology Fundamentals</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -1826,39 +1826,39 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>BK-IT04</t>
+          <t>BK-IT02</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Platform Technologies &amp; Web/Mobile</t>
+          <t>Applied AI &amp; Intelligent Technologies</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>KK5</t>
+          <t>KK1</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>BK-IT05</t>
+          <t>BK-IT03</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; Virtualization</t>
+          <t>Networking &amp; Communications</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -1870,953 +1870,1019 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>BK-IT06</t>
+          <t>BK-IT04</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Cybersecurity Principles &amp; Defense</t>
+          <t>Platform Technologies &amp; Web/Mobile</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>KK3, KK4</t>
+          <t>KK5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>BK-IT07</t>
+          <t>BK-IT05</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>System Integration and Architecture</t>
+          <t>Cloud Computing &amp; Virtualization</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>KK3, KK5</t>
+          <t>KK3</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>BK-IT08</t>
+          <t>BK-IT06</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>IT Service Management &amp; Governance</t>
+          <t>Cybersecurity Principles &amp; Defense</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>KK4</t>
+          <t>KK3, KK4</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>BK-IT09</t>
+          <t>BK-IT07</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Information Visualization</t>
+          <t>System Integration and Architecture</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>KK1, KK2</t>
+          <t>KK3, KK5</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>BK-IT10</t>
+          <t>BK-IT08</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>User Experience &amp; Interaction Design</t>
+          <t>IT Service Management &amp; Governance</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>KK5</t>
+          <t>KK4</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>BK-IT11</t>
+          <t>BK-IT09</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Software Development Practices</t>
+          <t>Data Analytics &amp; Information Visualization</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>KK5</t>
+          <t>KK1, KK2</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>BK-IT12</t>
+          <t>BK-IT10</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>IT Risk Management and Compliance</t>
+          <t>User Experience &amp; Interaction Design</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>KK4</t>
+          <t>KK5</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>BK-IT13</t>
+          <t>BK-IT11</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Technology Entrepreneurship</t>
+          <t>Software Development Practices</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>KK6</t>
+          <t>KK5</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>BK-IT12</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>IT Risk Management and Compliance</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>KK4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT13</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Technology Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>KK6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>BK-IT14</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>IoT and Embedded Smart Systems</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>KK1, KK3</t>
         </is>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT15</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Global Professional Practice</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>— *(membina `S1` &amp; `KU1`–`KU3`)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>KK1: Sistem Informasi Cerdas Berbasis AI/ML (Peminatan P1)</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="5" t="n"/>
-    </row>
-    <row r="78" ht="26" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Mampu menganalisis kebutuhan solusi cerdas berbasis AI/ML untuk proses bisnis organisasi.</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Laporan Analisis Kebutuhan Sistem Cerdas (STI-302 / STI-601).</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>Mampu merancang arsitektur sistem cerdas (NLP, Computer Vision, DSS, Conversational AI).</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Dokumen Desain Arsitektur AI (STA-01 / STA-05).</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Mampu mengembangkan prototipe aplikasi terintegrasi API inferensi AI secara fungsional.</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Repositori Kode Sumber dan Prototipe Aplikasi Cerdas (STI-601).</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>Mampu menguji dan mengevaluasi akurasi, efisiensi, dan keandalan model AI pada sistem.</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>Laporan Uji Kinerja &amp; Evaluasi Interoperabilitas AI.</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="86"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>KK2: Rekayasa Data &amp; MLOps (Peminatan P1)</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="5" t="n"/>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="5" t="n"/>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Mampu membangun pipeline akuisisi, praproses, dan transformasi data (ETL/ELT).</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Pipeline Data dengan Pandas/PySpark (STI-402 / STI-503).</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>Mampu melatih dan mengoptimasi model Machine Learning / Deep Learning.</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Model ML terlatih dengan evaluasi Confusion Matrix / F1-Score (STI-401 / STI-501).</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Mampu membangun dashboard Business Intelligence dan visualisasi data interaktif.</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>Dashboard BI interaktif di Tableau / Power BI / Streamlit (STI-402 / STI-503).</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>Mampu menerapkan pipeline MLOps untuk automasi deployment model AI (*Continuous Training*).</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>Pipeline CI/CD MLOps menggunakan MLflow / Docker (STA-04).</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="93"/>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>KK3: Cloud Infrastructure, IoT &amp; Cyber Defense (Peminatan P2)</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Mampu merancang dan mengelola arsitektur cloud terdistribusi (AWS/GCP/Azure).</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Topologi Cloud dan Konfigurasi Layanan IaaS/PaaS (STI-404 / STB-02).</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="9" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Mampu mengimplementasikan sistem IoT berbasis mikrokontroler dan protokol MQTT/CoAP.</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>Purwarupa Perangkat Keras ESP32 + Dashboard Telemetri (STI-504).</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Mampu menerapkan otomasi infrastruktur (CI/CD, Docker container, Kubernetes, Terraform).</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Pipeline CI/CD GitHub Actions &amp; Skrip IaC (STB-02).</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="9" t="inlineStr">
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>Mampu mengonfigurasi sistem pertahanan siber (Firewall, IDS/IPS, enkripsi SSL/TLS).</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>Laporan Konfigurasi Keamanan Jaringan (STI-603 / STB-01).</t>
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+    <row r="100"/>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>KK4: IT Governance, Risk Management &amp; Security Audit (Peminatan P2)</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="5" t="n"/>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="5" t="n"/>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Mampu menyusun kerangka kerja tata kelola TI berbasis standar COBIT 2019 / ITIL 4.</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Dokumen Desain Tata Kelola TI Organisasi (STB-04 / STB-05).</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="9" t="inlineStr">
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Mampu melakukan audit keamanan sistem informasi dan simulasi penetration testing beretika.</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-603 / STB-01).</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Mampu menyusun peta risiko TI (*Risk Register*) dan rencana mitigasi (ISO 27001 / ISO 31000).</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>Dokumen Manajemen Risiko &amp; Rencana Keberlangsungan Bisnis (STB-03).</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Mampu mengevaluasi keselarasan strategis investasi TI terhadap tujuan bisnis organisasi.</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>Laporan Evaluasi Enterprise Architecture TOGAF (STB-06).</t>
         </is>
       </c>
     </row>
-    <row r="104"/>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="107"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>KK5: UX/UI Design &amp; Digital Platform Engineering (Peminatan P3)</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n"/>
-      <c r="C105" s="4" t="n"/>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="5" t="n"/>
-    </row>
-    <row r="106" ht="26" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="5" t="n"/>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>Mampu melakukan riset pengguna (*UX Research*), pemetaan persona, dan perancangan *User Journey*.</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>Dokumen Riset UX dan *Empathy Map* (STI-303 / STC-01).</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>Mampu membangun prototipe UI interaktif *high-fidelity* berstandar *Design System*.</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>Prototipe Figma Interaktif dengan *Auto-Layout* &amp; Variabel (STI-303).</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>Mampu membangun aplikasi web frontend modern (SPA/SSR) dan backend API microservices.</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>Aplikasi Full-Stack Web di React/Vue/NodeJS/Go (STI-306 / STI-407 / STI-604).</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>Mampu merekayasa aplikasi mobile multiplatform dan sistem arsitektur multi-tenant SaaS.</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>Aplikasi Mobile Flutter/React Native &amp; Arsitektur SaaS (STI-505 / STC-05).</t>
         </is>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
+    <row r="114"/>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>KK6: Digital Technopreneurship &amp; Agile Project Management (Peminatan P3)</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="5" t="n"/>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="5" t="n"/>
+    </row>
+    <row r="116" ht="26" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Indikator Kinerja</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>Bukti Ketercapaian</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>Mampu memvalidasi problem-solution fit dan merancang model bisnis inovatif (*Lean Canvas*).</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>Dokumen *Business Model Canvas* &amp; Riset Validasi Pasar (STI-701 / MKU-204).</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>Mampu membangun dan meluncurkan produk minimum layak (*Minimum Viable Product / MVP*).</t>
         </is>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>Rilis MVP Digital yang teruji kepada pengguna awal (STI-701).</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>Mampu mengelola proyek rekayasa perangkat lunak menggunakan kerangka kerja Scrum/Agile.</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Manajemen *Product Backlog*, *Sprint*, dan *Burndown Chart* di Jira/Trello (STI-506).</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="9" t="inlineStr">
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Mampu menyusun *Pitch Deck* profesional dan mempresentasikan proposal bisnis ke calon investor.</t>
         </is>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>Dokumen *Pitch Deck* dan Presentasi *Demo Day* (STI-701 / STC-06).</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
+    <row r="121"/>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>5. PEMETAAN CPL KK → 4 PROFIL LULUSAN (PL)</t>
         </is>
       </c>
-      <c r="B119" s="4" t="n"/>
-      <c r="C119" s="4" t="n"/>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="5" t="n"/>
-    </row>
-    <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="5" t="n"/>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>Profil Lulusan</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Nomenklatur Profil Lulusan</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="G120" s="6" t="inlineStr">
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>**PL-1**</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>Intelligent IS Developer &amp; AI Engineer</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr"/>
-      <c r="F121" s="8" t="inlineStr"/>
-      <c r="G121" s="8" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr"/>
+      <c r="F124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr"/>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>**PL-2**</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>Cloud Infrastructure, Cybersecurity &amp; Smart Systems Integrator</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr"/>
-      <c r="D122" s="9" t="inlineStr"/>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr"/>
+      <c r="D125" s="9" t="inlineStr"/>
+      <c r="E125" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="F122" s="10" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="G122" s="10" t="inlineStr"/>
-      <c r="H122" s="10" t="inlineStr"/>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="G125" s="10" t="inlineStr"/>
+      <c r="H125" s="10" t="inlineStr"/>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>**PL-3**</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>UI/UX Designer &amp; Digital Platform Engineer</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr"/>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="8" t="inlineStr"/>
-      <c r="F123" s="8" t="inlineStr"/>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr"/>
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="8" t="inlineStr"/>
+      <c r="F126" s="8" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr">
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="9" t="inlineStr">
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>**PL-4**</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>Digital Technopreneur &amp; IT Product Innovator</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr"/>
-      <c r="E124" s="10" t="inlineStr"/>
-      <c r="F124" s="10" t="inlineStr"/>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr"/>
+      <c r="E127" s="10" t="inlineStr"/>
+      <c r="F127" s="10" t="inlineStr"/>
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="H124" s="10" t="inlineStr">
+      <c r="H127" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -2826,18 +2892,18 @@
   <mergeCells count="14">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A108:F108"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A119:H119"/>
+    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Laporan Analisis Kebutuhan Sistem Cerdas (STI-302 / STI-601).</t>
+          <t>Laporan Analisis Kebutuhan Sistem Cerdas (STI-307 / STI-624).</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Repositori Kode Sumber dan Prototipe Aplikasi Cerdas (STI-601).</t>
+          <t>Repositori Kode Sumber dan Prototipe Aplikasi Cerdas (STI-624).</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Pipeline Data dengan Pandas/PySpark (STI-402 / STI-503).</t>
+          <t>Pipeline Data dengan Pandas/PySpark (STI-415 / STI-520).</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Model ML terlatih dengan evaluasi Confusion Matrix / F1-Score (STI-401 / STI-501).</t>
+          <t>Model ML terlatih dengan evaluasi Confusion Matrix / F1-Score (STI-413 / STI-626).</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Dashboard BI interaktif di Tableau / Power BI / Streamlit (STI-402 / STI-503).</t>
+          <t>Dashboard BI interaktif di Tableau / Power BI / Streamlit (STI-415 / STI-520).</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Topologi Cloud dan Konfigurasi Layanan IaaS/PaaS (STI-404 / STB-02).</t>
+          <t>Topologi Cloud dan Konfigurasi Layanan IaaS/PaaS (STI-417 / STB-02).</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Purwarupa Perangkat Keras ESP32 + Dashboard Telemetri (STI-504).</t>
+          <t>Purwarupa Perangkat Keras ESP32 + Dashboard Telemetri (STI-521).</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Laporan Konfigurasi Keamanan Jaringan (STI-603 / STB-01).</t>
+          <t>Laporan Konfigurasi Keamanan Jaringan (STI-626 / STB-01).</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-603 / STB-01).</t>
+          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-626 / STB-01).</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Dokumen Riset UX dan *Empathy Map* (STI-303 / STC-01).</t>
+          <t>Dokumen Riset UX dan *Empathy Map* (STI-308 / STC-01).</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Prototipe Figma Interaktif dengan *Auto-Layout* &amp; Variabel (STI-303).</t>
+          <t>Prototipe Figma Interaktif dengan *Auto-Layout* &amp; Variabel (STI-308).</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Aplikasi Full-Stack Web di React/Vue/NodeJS/Go (STI-306 / STI-407 / STI-604).</t>
+          <t>Aplikasi Full-Stack Web di React/Vue/NodeJS/Go (STI-311 / STI-416 / STI-627).</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Aplikasi Mobile Flutter/React Native &amp; Arsitektur SaaS (STI-505 / STC-05).</t>
+          <t>Aplikasi Mobile Flutter/React Native &amp; Arsitektur SaaS (STI-522 / STC-05).</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Dokumen *Business Model Canvas* &amp; Riset Validasi Pasar (STI-701 / MKU-204).</t>
+          <t>Dokumen *Business Model Canvas* &amp; Riset Validasi Pasar (STI-728 / MKU-204).</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Rilis MVP Digital yang teruji kepada pengguna awal (STI-701).</t>
+          <t>Rilis MVP Digital yang teruji kepada pengguna awal (STI-728).</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Manajemen *Product Backlog*, *Sprint*, dan *Burndown Chart* di Jira/Trello (STI-506).</t>
+          <t>Manajemen *Product Backlog*, *Sprint*, dan *Burndown Chart* di Jira/Trello (STI-523).</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Dokumen *Pitch Deck* dan Presentasi *Demo Day* (STI-701 / STC-06).</t>
+          <t>Dokumen *Pitch Deck* dan Presentasi *Demo Day* (STI-728 / STC-06).</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Dokumen Desain Arsitektur AI (STA-01 / STA-05).</t>
+          <t>Dokumen Desain Arsitektur AI (STA-501 / STA-702).</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Pipeline CI/CD MLOps menggunakan MLflow / Docker (STA-04).</t>
+          <t>Pipeline CI/CD MLOps menggunakan MLflow / Docker (STA-701).</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Topologi Cloud dan Konfigurasi Layanan IaaS/PaaS (STI-417 / STB-02).</t>
+          <t>Topologi Cloud dan Konfigurasi Layanan IaaS/PaaS (STI-417 / STB-601).</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Pipeline CI/CD GitHub Actions &amp; Skrip IaC (STB-02).</t>
+          <t>Pipeline CI/CD GitHub Actions &amp; Skrip IaC (STB-601).</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Laporan Konfigurasi Keamanan Jaringan (STI-626 / STB-01).</t>
+          <t>Laporan Konfigurasi Keamanan Jaringan (STI-626 / STB-501).</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Dokumen Desain Tata Kelola TI Organisasi (STB-04 / STB-05).</t>
+          <t>Dokumen Desain Tata Kelola TI Organisasi (STB-701 / STB-702).</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-626 / STB-01).</t>
+          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-626 / STB-501).</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Dokumen Manajemen Risiko &amp; Rencana Keberlangsungan Bisnis (STB-03).</t>
+          <t>Dokumen Manajemen Risiko &amp; Rencana Keberlangsungan Bisnis (STB-602).</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Laporan Evaluasi Enterprise Architecture TOGAF (STB-06).</t>
+          <t>Laporan Evaluasi Enterprise Architecture TOGAF (STB-703).</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Dokumen Riset UX dan *Empathy Map* (STI-308 / STC-01).</t>
+          <t>Dokumen Riset UX dan *Empathy Map* (STI-308 / STC-501).</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Aplikasi Mobile Flutter/React Native &amp; Arsitektur SaaS (STI-522 / STC-05).</t>
+          <t>Aplikasi Mobile Flutter/React Native &amp; Arsitektur SaaS (STI-522 / STC-702).</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Dokumen *Pitch Deck* dan Presentasi *Demo Day* (STI-728 / STC-06).</t>
+          <t>Dokumen *Pitch Deck* dan Presentasi *Demo Day* (STI-728 / STC-703).</t>
         </is>
       </c>
     </row>
